--- a/catalogo_produtos.xlsx
+++ b/catalogo_produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcio.silva\Documents\GitHub\catalogo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C21CDA21-1A52-4A18-941A-E0AE6B9B448B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08718DD0-9B87-4A68-91A5-6B54C7E140CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{9FDC799A-A518-4814-A51D-97AF7748B86C}"/>
   </bookViews>
